--- a/data/export/2026-09-17-浦东78路.xlsx
+++ b/data/export/2026-09-17-浦东78路.xlsx
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -642,19 +642,19 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：06:20采样，终点ETA 76分钟</t>
+          <t>SHMAAS末次终点ETA推算：07:18采样，终点ETA 27分钟</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +689,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -753,24 +757,24 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±8分钟</t>
+          <t>07:10采样：该车到重点站五莲路凌河路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -780,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -809,7 +813,7 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
@@ -829,12 +833,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -872,24 +876,24 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>109分钟</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数109分钟估算，约±15分钟</t>
+          <t>07:18采样：该车到重点站五莲路东陆路 ETA 27分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -899,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -923,12 +927,12 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
@@ -948,12 +952,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -961,22 +965,22 @@
       <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>06:50</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1009,12 +1013,12 @@
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1028,7 +1032,7 @@
       <c r="T5" s="2" t="inlineStr"/>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -1064,7 +1068,1419 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>07:10采样：该车到重点站张杨北路博兴路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>07:10采样：该车到重点站花山路杨高北路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>96分钟</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>07:10采样：该车到重点站张杨北路博兴路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>101分钟</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数101分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-浦东78路.xlsx
+++ b/data/export/2026-09-17-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -451,7 +451,7 @@
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="14" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
     <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
@@ -642,19 +642,19 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：07:18采样，终点ETA 27分钟</t>
+          <t>SHMAAS末次终点ETA推算：07:30采样，终点ETA 20分钟</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -757,26 +757,22 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>112分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>07:10采样：该车到重点站五莲路凌河路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:10采样，终点ETA 7分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -784,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -813,7 +809,7 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
@@ -823,22 +819,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -876,26 +872,22 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98分钟</t>
+          <t>115分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>07:18采样：该车到重点站五莲路东陆路 ETA 27分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 15分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -903,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -932,7 +924,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
@@ -942,22 +934,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -990,27 +982,31 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1018,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1042,33 +1038,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1101,29 +1101,29 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>07:10采样：该车到重点站张杨北路博兴路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
@@ -1172,22 +1172,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1298,7 +1298,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1336,19 +1336,19 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>07:10采样：该车到重点站花山路杨高北路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
+          <t>07:50采样：该车到重点站五莲路凌河路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1412,12 +1412,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1450,29 +1450,29 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>07:10采样：该车到重点站张杨北路博兴路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1506,12 +1506,12 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
@@ -1521,22 +1521,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1574,19 +1574,19 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±5分钟</t>
+          <t>07:20采样：该车到重点站杨高北路夏碧路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1693,19 +1693,19 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 35分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1740,33 +1740,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1804,19 +1808,19 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±5分钟</t>
+          <t>07:50采样：该车到重点站金高路行泰路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1831,7 +1835,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1860,7 +1864,7 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
@@ -1880,12 +1884,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1923,24 +1927,24 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±8分钟</t>
+          <t>08:20采样：该车到重点站杨高北路（外高桥保税区南站） ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数26分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1950,7 +1954,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1979,7 +1983,7 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
@@ -1999,12 +2003,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -2042,24 +2046,24 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数101分钟估算，约±6分钟</t>
+          <t>08:00采样：该车到重点站金高路俱进路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2069,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2098,7 +2102,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
@@ -2118,12 +2122,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -2161,24 +2165,24 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±8分钟</t>
+          <t>08:10采样：该车到重点站金高路万安街 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2188,7 +2192,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2217,7 +2221,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
@@ -2237,12 +2241,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2280,24 +2284,24 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±5分钟</t>
+          <t>08:10采样：该车到重点站金高路源华路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2307,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2336,7 +2340,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
@@ -2356,12 +2360,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2369,24 +2373,24 @@
       <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>08:03</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -2399,19 +2403,19 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±5分钟</t>
+          <t>08:20采样：该车到重点站杨高北路航津路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2426,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2440,47 +2444,1106 @@
       <c r="T17" s="2" t="inlineStr"/>
       <c r="U17" s="2" t="inlineStr">
         <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>08:03</t>
         </is>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>08:20采样：该车到重点站张杨北路金桥路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W17" s="2" t="inlineStr">
+      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X17" s="2" t="inlineStr">
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>95.5</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>97分钟</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>08:20采样：该车到重点站杨高北路航津路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y17" s="2" t="inlineStr">
+      <c r="Y21" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z17" s="2" t="inlineStr">
+      <c r="Z21" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
+      <c r="AA21" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>89.5</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr">
-        <is>
-          <t>6/15</t>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>96.5</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>100分钟</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数100分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-浦东78路.xlsx
+++ b/data/export/2026-09-17-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:AC35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,22 +819,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -877,14 +877,14 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>115分钟</t>
+          <t>116分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 15分钟</t>
+          <t>SHMAAS末次终点ETA推算：08:30采样，终点ETA 5分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr"/>
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -944,12 +944,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1058,17 +1058,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1225,19 +1225,19 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>113分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：08:30采样，终点ETA 12分钟</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr"/>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1272,33 +1272,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1336,24 +1340,24 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>110分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>07:50采样：该车到重点站五莲路凌河路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
+          <t>同车下一次反向发车08:57，减去该车自身同类时段历史终点停站中位数8分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1363,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1392,7 +1396,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
@@ -1402,22 +1406,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1455,24 +1459,24 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1482,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1531,12 +1535,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1569,24 +1573,24 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>113分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站杨高北路夏碧路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1601,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1625,12 +1629,12 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
@@ -1640,22 +1644,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1688,27 +1692,31 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 35分钟</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -1716,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1740,12 +1748,12 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
@@ -1765,12 +1773,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1803,29 +1811,29 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>116分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>07:50采样：该车到重点站金高路行泰路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1835,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1859,12 +1867,12 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
@@ -1874,22 +1882,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1922,29 +1930,29 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站杨高北路（外高桥保税区南站） ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数26分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1954,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1978,12 +1986,12 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
@@ -1993,22 +2001,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2046,26 +2054,22 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>105分钟</t>
+          <t>106分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>08:00采样：该车到重点站金高路俱进路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:10采样，终点ETA 6分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2073,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2102,7 +2106,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
@@ -2112,22 +2116,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2246,7 +2250,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2284,26 +2288,22 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站金高路源华路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±7分钟</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:10采样，终点ETA 13分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
@@ -2350,22 +2350,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2403,24 +2403,24 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站杨高北路航津路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
+          <t>同车下一次反向发车09:45，减去该车自身同类时段历史终点停站中位数10分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
@@ -2469,17 +2469,17 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2517,29 +2517,29 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站张杨北路金桥路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2641,19 +2641,19 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>111分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站杨高北路航津路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
+          <t>09:10采样：该车到重点站杨高中路云山路 ETA 33分钟；叠加该车自身同类时段从该站到终点历史中位数14分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -2760,22 +2760,26 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>09:20采样：该车到重点站金杨路金口路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数20分钟，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -2783,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2807,17 +2811,17 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -2827,17 +2831,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2875,26 +2879,22 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±9分钟</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:20采样，终点ETA 26分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
@@ -2941,22 +2941,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2994,24 +2994,24 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±14分钟</t>
+          <t>09:20采样：该车到重点站金高路俱进路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3419,12 +3419,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3432,24 +3432,24 @@
       <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3462,19 +3462,19 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数100分钟估算，约±5分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数94分钟估算，约±5分钟</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3503,47 +3503,1110 @@
       <c r="T26" s="2" t="inlineStr"/>
       <c r="U26" s="2" t="inlineStr">
         <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>102分钟</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数102分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>09:05</t>
         </is>
       </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>98分钟</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>09:20采样：该车到重点站杨高北路夏碧路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W26" s="2" t="inlineStr">
+      <c r="W28" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X26" s="2" t="inlineStr">
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>09:20采样：该车到重点站金杨路枣庄路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数72分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y26" s="2" t="inlineStr">
+      <c r="Y31" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr">
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
         <is>
           <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>92.5</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>92.5</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-浦东78路.xlsx
+++ b/data/export/2026-09-17-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC35"/>
+  <dimension ref="A1:AC42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -934,22 +934,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1053,22 +1053,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1172,22 +1172,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1406,22 +1406,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1525,22 +1525,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1763,22 +1763,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,22 +1882,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2398,29 +2398,29 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>102分钟</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车09:45，减去该车自身同类时段历史终点停站中位数10分钟，约±7分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2636,29 +2636,29 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>111分钟</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>09:10采样：该车到重点站杨高中路云山路 ETA 33分钟；叠加该车自身同类时段从该站到终点历史中位数14分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -2760,24 +2760,24 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>09:20采样：该车到重点站金杨路金口路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数20分钟，约±9分钟</t>
+          <t>09:40采样：该车到重点站丁香路民生路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数3分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -2874,27 +2874,31 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：09:20采样，终点ETA 26分钟</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2902,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2926,12 +2930,12 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
@@ -2951,7 +2955,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -2994,26 +2998,22 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>09:20采样：该车到重点站金高路俱进路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:50采样，终点ETA 8分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3108,27 +3108,31 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3136,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3160,37 +3164,37 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3223,29 +3227,29 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±13分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3255,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3279,12 +3283,12 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
@@ -3294,22 +3298,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3342,27 +3346,31 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3370,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3394,37 +3402,37 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3457,24 +3465,24 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数94分钟估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3489,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3513,12 +3521,12 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
@@ -3538,12 +3546,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3576,29 +3584,29 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>102分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数102分钟估算，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3608,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3632,12 +3640,12 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
@@ -3647,22 +3655,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3695,29 +3703,29 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>98分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>09:20采样：该车到重点站杨高北路夏碧路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3727,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3751,12 +3759,12 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
@@ -3766,22 +3774,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3814,29 +3822,29 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>09:20采样：该车到重点站金杨路枣庄路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数72分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3846,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3870,12 +3878,12 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
@@ -3895,7 +3903,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3938,19 +3946,19 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：10:20采样，终点ETA 20分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr"/>
@@ -3961,7 +3969,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3985,17 +3993,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -4005,17 +4013,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4053,24 +4061,24 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±5分钟</t>
+          <t>同车下一次反向发车11:10，减去该车自身同类时段历史终点停站中位数6分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -4080,7 +4088,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4109,7 +4117,7 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
@@ -4119,22 +4127,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -4172,19 +4180,19 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±5分钟</t>
+          <t>10:20采样：该车到重点站花山路杨高北路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数12分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -4199,7 +4207,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4228,7 +4236,7 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
@@ -4248,12 +4256,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4368,7 +4376,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4406,19 +4414,19 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±5分钟</t>
+          <t>10:20采样：该车到重点站金高路行泰路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -4433,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4462,7 +4470,7 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
@@ -4482,7 +4490,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4525,24 +4533,24 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±14分钟</t>
+          <t>10:20采样：该车到重点站金高路东靖路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4552,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4576,37 +4584,866 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>10:20采样：该车到重点站云山路灵山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数70分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>84.3</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>10:20采样：该车到重点站五莲路凌河路 ETA 31分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>84.7</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="X35" s="2" t="inlineStr">
+      <c r="X38" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y35" s="2" t="inlineStr">
+      <c r="Y38" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z35" s="2" t="inlineStr">
+      <c r="Z38" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
+      <c r="AA38" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>97.0</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr">
-        <is>
-          <t>9/18</t>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>94分钟</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数94分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>91.7</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>91.7</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>96.3</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>18/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-浦东78路.xlsx
+++ b/data/export/2026-09-17-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AC49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,22 +819,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -934,17 +934,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1525,22 +1525,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,22 +2001,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2116,22 +2116,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2350,22 +2350,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2479,12 +2479,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2826,17 +2826,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2945,22 +2945,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3298,17 +3298,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3827,24 +3827,24 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3903,12 +3903,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3941,27 +3941,31 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：10:20采样，终点ETA 20分钟</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -3969,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3993,12 +3997,12 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
@@ -4008,22 +4012,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4056,29 +4060,29 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>104分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车11:10，减去该车自身同类时段历史终点停站中位数6分钟，约±8分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -4088,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4112,12 +4116,12 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
@@ -4137,7 +4141,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4175,12 +4179,12 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -4192,12 +4196,12 @@
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站花山路杨高北路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数12分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -4207,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4231,12 +4235,12 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
@@ -4246,22 +4250,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4294,27 +4298,31 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4322,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4346,37 +4354,37 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4417,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4419,14 +4427,14 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站金高路行泰路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -4441,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4465,12 +4473,12 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
@@ -4490,12 +4498,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4528,29 +4536,29 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站金高路东靖路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4560,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4584,12 +4592,12 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
@@ -4599,22 +4607,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4647,29 +4655,29 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站云山路灵山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数70分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4679,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4703,12 +4711,12 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
@@ -4718,17 +4726,17 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4771,24 +4779,24 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站五莲路凌河路 ETA 31分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
+          <t>10:40采样：该车到重点站五莲路荷泽路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4798,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4847,12 +4855,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4885,29 +4893,29 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±12分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4917,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4941,12 +4949,12 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
@@ -4956,17 +4964,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5004,29 +5012,29 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数94分钟估算，约±12分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5036,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5060,12 +5068,12 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
@@ -5075,22 +5083,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5128,19 +5136,19 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+          <t>11:00采样：该车到重点站五莲路凌河路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -5155,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5184,7 +5192,7 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
@@ -5204,12 +5212,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5247,24 +5255,24 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±14分钟</t>
+          <t>11:20采样：该车到重点站金高路俱进路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -5274,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5303,7 +5311,7 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
@@ -5323,7 +5331,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5336,24 +5344,24 @@
       <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5366,22 +5374,26 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>11:20采样：该车到重点站巨峰路成园路 ETA 20分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -5389,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5403,47 +5415,876 @@
       <c r="T42" s="2" t="inlineStr"/>
       <c r="U42" s="2" t="inlineStr">
         <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>85.3</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
           <t>11:10</t>
         </is>
       </c>
-      <c r="V42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W42" s="2" t="inlineStr">
+      <c r="W43" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X42" s="2" t="inlineStr">
+      <c r="X43" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y42" s="2" t="inlineStr">
+      <c r="Y43" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z42" s="2" t="inlineStr">
+      <c r="Z43" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
+      <c r="AA43" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB42" s="2" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
-      <c r="AC42" s="2" t="inlineStr">
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
         <is>
           <t>18/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>88.7</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>89.7</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>93.2</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>83.2</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>91.8</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>87.8</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-浦东78路.xlsx
+++ b/data/export/2026-09-17-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC49"/>
+  <dimension ref="A1:AC54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -944,12 +944,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1406,22 +1406,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,22 +1882,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,17 +2001,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2116,17 +2116,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2350,22 +2350,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3655,22 +3655,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4012,17 +4012,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4131,22 +4131,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4250,17 +4250,17 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4369,22 +4369,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4541,24 +4541,24 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4898,24 +4898,24 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5017,24 +5017,24 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5250,12 +5250,12 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站金高路俱进路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5306,12 +5306,12 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
@@ -5321,22 +5321,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5369,29 +5369,29 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站巨峰路成园路 ETA 20分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
@@ -5440,17 +5440,17 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5488,27 +5488,31 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -5516,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5540,37 +5544,37 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -5603,7 +5607,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -5620,12 +5624,12 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5635,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5659,12 +5663,12 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
@@ -5674,22 +5678,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5722,29 +5726,29 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5754,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5778,12 +5782,12 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
@@ -5793,17 +5797,17 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5846,24 +5850,24 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±10分钟</t>
+          <t>12:21采样：该车到重点站金高路行泰路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5873,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5902,7 +5906,7 @@
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
@@ -5922,7 +5926,7 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -5965,7 +5969,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -5977,12 +5981,12 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±6分钟</t>
+          <t>12:21采样：该车到重点站杨高北路航津路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5992,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6021,7 +6025,7 @@
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
@@ -6084,19 +6088,19 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+          <t>12:21采样：该车到重点站五莲路凌河路 ETA 24分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -6111,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6140,7 +6144,7 @@
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
@@ -6160,12 +6164,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6279,12 +6283,603 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
           <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>92.2</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>85.7</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-浦东78路.xlsx
+++ b/data/export/2026-09-17-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC54"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,22 +704,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,17 +819,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -934,22 +934,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1411,17 +1411,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1525,22 +1525,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2588,22 +2588,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2826,17 +2826,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2945,17 +2945,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3298,22 +3298,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3660,17 +3660,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4017,17 +4017,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4379,12 +4379,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4607,17 +4607,17 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4726,17 +4726,17 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4964,22 +4964,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5083,22 +5083,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5326,17 +5326,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5445,17 +5445,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5569,12 +5569,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -5612,24 +5612,24 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5731,24 +5731,24 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5845,7 +5845,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站金高路行泰路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
@@ -5916,17 +5916,17 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -5964,29 +5964,29 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站杨高北路航津路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
@@ -6035,17 +6035,17 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站五莲路凌河路 ETA 24分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6139,12 +6139,12 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
@@ -6154,22 +6154,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6207,26 +6207,22 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：13:10采样，终点ETA 42分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6234,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6258,12 +6254,12 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
@@ -6273,22 +6269,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6326,26 +6322,22 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：13:20采样，终点ETA 47分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6353,7 +6345,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6377,17 +6369,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6397,17 +6389,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6445,22 +6437,26 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>13:20采样：该车到重点站巨峰路成园路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -6468,7 +6464,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6492,17 +6488,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6512,17 +6508,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6560,24 +6556,24 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±8分钟</t>
+          <t>13:20采样：该车到重点站金杨路枣庄路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6587,7 +6583,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6616,7 +6612,7 @@
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
@@ -6636,12 +6632,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -6679,19 +6675,19 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+          <t>13:20采样：该车到重点站金高路俱进路 ETA 27分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -6706,7 +6702,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6735,7 +6731,7 @@
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
@@ -6755,12 +6751,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6821,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6874,12 +6870,603 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>94分钟</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数94分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>92.6</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>81.5</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>88.8</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
           <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>94分钟</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数94分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>89.4</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-浦东78路.xlsx
+++ b/data/export/2026-09-17-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>92.6</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -944,12 +944,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1058,12 +1058,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1406,22 +1406,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,22 +2001,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2235,22 +2235,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2831,12 +2831,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>92.6</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3655,22 +3655,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4012,22 +4012,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4379,12 +4379,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4617,12 +4617,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>92.6</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4731,12 +4731,12 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5321,22 +5321,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5440,22 +5440,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>92.6</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6040,12 +6040,12 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6202,27 +6202,31 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：13:10采样，终点ETA 42分钟</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6230,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6254,12 +6258,12 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
@@ -6279,7 +6283,7 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6317,7 +6321,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -6334,10 +6338,14 @@
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：13:20采样，终点ETA 47分钟</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6345,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6369,37 +6377,37 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6432,29 +6440,29 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>13:20采样：该车到重点站巨峰路成园路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6464,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6488,12 +6496,12 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
@@ -6503,22 +6511,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6551,29 +6559,29 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>13:20采样：该车到重点站金杨路枣庄路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6583,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6607,12 +6615,12 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
@@ -6632,7 +6640,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6670,29 +6678,29 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>13:20采样：该车到重点站金高路俱进路 ETA 27分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6702,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6726,12 +6734,12 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
@@ -6751,12 +6759,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6794,19 +6802,19 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±5分钟</t>
+          <t>14:00采样：该车到重点站巨峰路成园路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -6821,7 +6829,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6850,7 +6858,7 @@
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
@@ -6870,12 +6878,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6913,24 +6921,24 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数94分钟估算，约±14分钟</t>
+          <t>14:00采样：该车到重点站金高路俱进路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数71分钟，约±15分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6940,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6969,7 +6977,7 @@
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
@@ -6989,12 +6997,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>92.6</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7032,22 +7040,26 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>14:00采样：该车到重点站金杨路枣庄路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7055,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7079,17 +7091,17 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7099,12 +7111,12 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7147,24 +7159,24 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±11分钟</t>
+          <t>14:00采样：该车到重点站杨高北路夏碧路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±14分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7174,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7203,7 +7215,7 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
@@ -7223,12 +7235,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7293,7 +7305,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7347,7 +7359,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7424,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7461,12 +7473,369 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
           <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>92.4</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>84.2</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>75分钟</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-浦东78路.xlsx
+++ b/data/export/2026-09-17-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC62"/>
+  <dimension ref="A1:AC63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -824,17 +824,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -939,17 +939,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,22 +1882,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2950,17 +2950,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3303,17 +3303,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4131,22 +4131,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4612,17 +4612,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5559,22 +5559,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5921,17 +5921,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6159,17 +6159,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6564,24 +6564,24 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6630,22 +6630,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -6683,24 +6683,24 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6797,29 +6797,29 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>14:00采样：该车到重点站巨峰路成园路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6829,7 +6829,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
@@ -6878,12 +6878,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6921,26 +6921,22 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>102分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>14:00采样：该车到重点站金高路俱进路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数71分钟，约±15分钟</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：14:20采样，终点ETA 49分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -6948,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6972,17 +6968,17 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -6992,17 +6988,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7040,24 +7036,24 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>67分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>14:00采样：该车到重点站金杨路枣庄路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±5分钟</t>
+          <t>14:20采样：该车到重点站五莲路凌河路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -7067,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7091,7 +7087,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
@@ -7116,7 +7112,7 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7159,26 +7155,22 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>14:00采样：该车到重点站杨高北路夏碧路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±14分钟</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：14:10采样，终点ETA 78分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -7186,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7210,17 +7202,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7230,17 +7222,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7305,7 +7297,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7359,7 +7351,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7424,7 +7416,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7478,7 +7470,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7543,7 +7535,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7597,7 +7589,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7662,7 +7654,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7724,24 +7716,24 @@
       <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7754,34 +7746,30 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±6分钟</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7795,45 +7783,164 @@
       <c r="T62" s="2" t="inlineStr"/>
       <c r="U62" s="2" t="inlineStr">
         <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>96.2</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="V62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>75分钟</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W62" s="2" t="inlineStr">
+      <c r="W63" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X62" s="2" t="inlineStr">
+      <c r="X63" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y62" s="2" t="inlineStr">
+      <c r="Y63" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z62" s="2" t="inlineStr">
+      <c r="Z63" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
+      <c r="AA63" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB62" s="2" t="inlineStr">
+      <c r="AB63" s="2" t="inlineStr">
         <is>
           <t>85.0</t>
         </is>
       </c>
-      <c r="AC62" s="2" t="inlineStr">
+      <c r="AC63" s="2" t="inlineStr">
         <is>
           <t>3/18</t>
         </is>

--- a/data/export/2026-09-17-浦东78路.xlsx
+++ b/data/export/2026-09-17-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC63"/>
+  <dimension ref="A1:AC72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -449,11 +449,11 @@
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,22 +819,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -939,17 +939,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1053,12 +1053,12 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1172,22 +1172,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1287,22 +1287,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1535,12 +1535,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1644,22 +1644,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1887,17 +1887,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>94.6</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2011,12 +2011,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2116,22 +2116,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2350,22 +2350,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2469,22 +2469,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2707,22 +2707,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2945,22 +2945,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3179,22 +3179,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3303,17 +3303,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3536,22 +3536,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3893,22 +3893,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4022,12 +4022,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4136,17 +4136,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>94.6</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4250,22 +4250,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4369,22 +4369,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4488,22 +4488,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4607,22 +4607,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
@@ -4769,36 +4769,32 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程28%处后消失；随后反向物理轨迹由seq27推进至seq37，推进10站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>10:40采样：该车到重点站五莲路荷泽路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±6分钟</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -4806,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4814,10 +4810,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q37" s="2" t="inlineStr"/>
-      <c r="R37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金桥路</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
       <c r="S37" s="2" t="inlineStr"/>
-      <c r="T37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq12映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
           <t>10:20</t>
@@ -4830,37 +4838,37 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4969,17 +4977,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5093,12 +5101,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5217,7 +5225,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5336,7 +5344,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5450,12 +5458,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5564,17 +5572,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>94.6</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5678,22 +5686,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5758,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5797,22 +5805,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5916,22 +5924,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5996,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6035,12 +6043,12 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
@@ -6115,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6159,17 +6167,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6283,12 +6291,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6353,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6407,7 +6415,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6521,12 +6529,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6635,17 +6643,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>94.6</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -6683,19 +6691,19 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -6710,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6749,22 +6757,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6802,24 +6810,24 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6829,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6868,22 +6876,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6916,7 +6924,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -6933,10 +6941,14 @@
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：14:20采样，终点ETA 49分钟</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -6944,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6968,37 +6980,37 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7031,29 +7043,29 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>14:20采样：该车到重点站五莲路凌河路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -7063,7 +7075,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7087,12 +7099,12 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
@@ -7102,12 +7114,12 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
@@ -7150,27 +7162,31 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：14:10采样，终点ETA 78分钟</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -7178,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7202,17 +7218,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7222,17 +7238,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7270,26 +7286,22 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±12分钟</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：15:20采样，终点ETA 30分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -7297,7 +7309,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7326,7 +7338,7 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
@@ -7346,12 +7358,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -7384,29 +7396,29 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数94分钟估算，约±14分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7416,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7440,12 +7452,12 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
@@ -7465,12 +7477,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7520,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -7520,12 +7532,12 @@
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±14分钟</t>
+          <t>15:20采样：该车到重点站五莲路荷泽路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数30分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7535,7 +7547,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7559,12 +7571,12 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
@@ -7589,7 +7601,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -7622,29 +7634,29 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7654,7 +7666,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7678,12 +7690,12 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
@@ -7703,12 +7715,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7746,22 +7758,26 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>15:20采样：该车到重点站巨峰路成园路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -7769,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7793,17 +7809,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7813,17 +7829,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>94.6</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -7861,24 +7877,24 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±6分钟</t>
+          <t>15:20采样：该车到重点站五莲路荷泽路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7888,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7917,32 +7933,1103 @@
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>75分钟</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>15:20采样：该车到重点站金高路俱进路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>15:20采样：该车到重点站杨高北路夏碧路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>91.3</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>15:20采样：该车到重点站金杨路枣庄路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>84.8</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>76分钟</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y63" s="2" t="inlineStr">
+      <c r="Y67" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z63" s="2" t="inlineStr">
+      <c r="Z67" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
+      <c r="AA67" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB63" s="2" t="inlineStr">
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>87.6</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
         <is>
           <t>85.0</t>
         </is>
       </c>
-      <c r="AC63" s="2" t="inlineStr">
+      <c r="AC69" s="2" t="inlineStr">
         <is>
           <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-浦东78路.xlsx
+++ b/data/export/2026-09-17-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC72"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,22 +704,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -934,22 +934,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1287,22 +1287,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1406,22 +1406,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1525,22 +1525,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1763,22 +1763,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,14 +1882,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>94.6</t>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,17 +2001,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2235,22 +2235,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2479,12 +2479,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2588,22 +2588,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3298,22 +3298,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3536,22 +3536,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3655,22 +3655,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3774,22 +3774,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3903,12 +3903,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4012,17 +4012,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4131,14 +4131,14 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
           <t>94.6</t>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4617,12 +4617,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4972,22 +4972,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5091,22 +5091,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5134,36 +5134,32 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq23推进至seq37，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>11:00采样：该车到重点站五莲路凌河路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -5171,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5179,10 +5175,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q40" s="2" t="inlineStr"/>
-      <c r="R40" s="2" t="inlineStr"/>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>巨峰路五莲路</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="S40" s="2" t="inlineStr"/>
-      <c r="T40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq20映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
           <t>10:45</t>
@@ -5195,37 +5203,37 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5329,22 +5337,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5448,17 +5456,17 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5528,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5567,14 +5575,14 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
           <t>94.6</t>
@@ -5582,7 +5590,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5686,17 +5694,17 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5766,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5815,12 +5823,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5934,12 +5942,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6053,7 +6061,7 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6123,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6162,22 +6170,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6281,22 +6289,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6400,22 +6408,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6519,17 +6527,17 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6599,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6638,14 +6646,14 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
           <t>94.6</t>
@@ -6653,7 +6661,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6757,17 +6765,17 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6837,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6886,12 +6894,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7005,12 +7013,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7075,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7124,7 +7132,7 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7194,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7233,22 +7241,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7281,27 +7289,31 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：15:20采样，终点ETA 30分钟</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -7309,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7333,12 +7345,12 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
@@ -7348,22 +7360,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7401,24 +7413,24 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7428,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7467,22 +7479,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7515,12 +7527,12 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -7532,12 +7544,12 @@
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>15:20采样：该车到重点站五莲路荷泽路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数30分钟，约±7分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7547,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7571,12 +7583,12 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
@@ -7586,22 +7598,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7639,24 +7651,24 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7666,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7705,17 +7717,17 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7753,12 +7765,12 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -7770,12 +7782,12 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>15:20采样：该车到重点站巨峰路成园路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±10分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7785,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7809,12 +7821,12 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
@@ -7824,14 +7836,14 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
           <t>94.6</t>
@@ -7839,7 +7851,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -7872,29 +7884,29 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>15:20采样：该车到重点站五莲路荷泽路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±9分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7904,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7928,12 +7940,12 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
@@ -7943,22 +7955,22 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7991,29 +8003,29 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>15:20采样：该车到重点站金高路俱进路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±7分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8023,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8047,12 +8059,12 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
@@ -8062,22 +8074,22 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8115,26 +8127,22 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>15:20采样：该车到重点站杨高北路夏碧路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：16:20采样，终点ETA 16分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -8142,7 +8150,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8171,7 +8179,7 @@
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
@@ -8191,12 +8199,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -8229,29 +8237,29 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>15:20采样：该车到重点站金杨路枣庄路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8261,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8285,12 +8293,12 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
@@ -8300,17 +8308,17 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8353,26 +8361,22 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：16:20采样，终点ETA 14分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -8380,7 +8384,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8409,7 +8413,7 @@
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
@@ -8429,12 +8433,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8472,24 +8476,24 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±7分钟</t>
+          <t>16:20采样：该车到重点站云山路灵山路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数11分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8499,7 +8503,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8528,7 +8532,7 @@
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
@@ -8548,12 +8552,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8591,24 +8595,24 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±7分钟</t>
+          <t>16:20采样：该车到重点站杨高北路（外高桥保税区南站） ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数25分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8618,7 +8622,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8647,7 +8651,7 @@
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
@@ -8667,12 +8671,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -8710,24 +8714,24 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±12分钟</t>
+          <t>16:20采样：该车到重点站五莲路归昌路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8737,7 +8741,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8761,12 +8765,12 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
@@ -8786,12 +8790,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8829,24 +8833,24 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±10分钟</t>
+          <t>16:20采样：该车到重点站五莲路凌河路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8856,7 +8860,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8885,7 +8889,7 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
@@ -8905,12 +8909,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8918,24 +8922,24 @@
       <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -8948,34 +8952,34 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±6分钟</t>
+          <t>16:20采样：该车到重点站五莲路凌河路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9004,32 +9008,1206 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>92.3</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>16:20采样：该车到重点站金高路东靖路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y72" s="2" t="inlineStr">
+      <c r="Y74" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z72" s="2" t="inlineStr">
+      <c r="Z74" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
+      <c r="AA74" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AB72" s="2" t="inlineStr">
-        <is>
-          <t>82.0</t>
-        </is>
-      </c>
-      <c r="AC72" s="2" t="inlineStr">
-        <is>
-          <t>1/18</t>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>96分钟</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>16:20采样：该车到重点站花山路大同路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数82分钟，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>88.2</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>91.2</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>90.5</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>83.8</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>18:18</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>98分钟</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数98分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>89.7</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>94.6</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>18/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>83.4</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>91.3</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-浦东78路.xlsx
+++ b/data/export/2026-09-17-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,17 +819,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -944,12 +944,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1172,22 +1172,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1525,22 +1525,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1644,22 +1644,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2006,12 +2006,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2116,22 +2116,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2469,22 +2469,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2707,22 +2707,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2826,17 +2826,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2945,17 +2945,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3179,22 +3179,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3893,22 +3893,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4250,22 +4250,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4488,22 +4488,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4607,17 +4607,17 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4726,17 +4726,17 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4853,22 +4853,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5091,22 +5091,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5228,12 +5228,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5813,22 +5813,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5932,17 +5932,17 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6051,17 +6051,17 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6289,22 +6289,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6418,12 +6418,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6884,22 +6884,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7003,17 +7003,17 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7122,17 +7122,17 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7370,12 +7370,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7479,22 +7479,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7965,12 +7965,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8122,27 +8122,31 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：16:20采样，终点ETA 16分钟</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -8150,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8174,12 +8178,12 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
@@ -8189,22 +8193,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8254,12 +8258,12 @@
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8269,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8356,27 +8360,31 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：16:20采样，终点ETA 14分钟</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -8384,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8408,12 +8416,12 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
@@ -8423,22 +8431,22 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8471,24 +8479,24 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站云山路灵山路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数11分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -8503,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8527,12 +8535,12 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
@@ -8542,22 +8550,22 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8590,24 +8598,24 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站杨高北路（外高桥保税区南站） ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数25分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
@@ -8622,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8646,12 +8654,12 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
@@ -8661,22 +8669,22 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA69" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8709,29 +8717,29 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站五莲路归昌路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±6分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8741,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8765,12 +8773,12 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
@@ -8780,22 +8788,22 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8828,29 +8836,29 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站五莲路凌河路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8860,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8884,12 +8892,12 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
@@ -8899,17 +8907,17 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8947,24 +8955,24 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站五莲路凌河路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -8979,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9003,12 +9011,12 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
@@ -9018,7 +9026,7 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9028,12 +9036,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -9066,29 +9074,29 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站金高路东靖路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±8分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -9098,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9122,12 +9130,12 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
@@ -9137,17 +9145,17 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9190,19 +9198,19 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±5分钟</t>
+          <t>17:20采样：该车到重点站大同路石家街（市七医院） ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数10分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
@@ -9217,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9246,7 +9254,7 @@
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
@@ -9266,12 +9274,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9309,26 +9317,22 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站花山路大同路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数82分钟，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：17:20采样，终点ETA 27分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9336,7 +9340,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9360,12 +9364,12 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
@@ -9375,22 +9379,22 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9428,24 +9432,24 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±12分钟</t>
+          <t>17:20采样：该车到重点站大同路石家街（市七医院） ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数9分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -9455,7 +9459,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9479,12 +9483,12 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
@@ -9504,12 +9508,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9547,19 +9551,19 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±5分钟</t>
+          <t>17:20采样：该车到重点站金高路俱进路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
@@ -9574,7 +9578,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9603,7 +9607,7 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
@@ -9623,12 +9627,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -9666,22 +9670,26 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>17:20采样：该车到重点站五莲路荷泽路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -9689,7 +9697,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9713,17 +9721,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9733,12 +9741,12 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9781,19 +9789,19 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>98分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数98分钟估算，约±5分钟</t>
+          <t>17:20采样：该车到重点站巨峰路成园路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -9808,7 +9816,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9837,7 +9845,7 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
@@ -9857,12 +9865,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9923,7 +9931,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10038,7 +10046,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10153,7 +10161,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10207,7 +10215,1062 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>18:37</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>93分钟</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>17:20采样：该车到重点站金杨路枣庄路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数72分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>101分钟</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>17:20采样：该车到重点站金高路俱进路 ETA 25分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>92.3</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>96分钟</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数96分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>19:04</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>100分钟</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数100分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>81.8</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>92.3</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>92.7</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
           <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>88.3</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-浦东78路.xlsx
+++ b/data/export/2026-09-17-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC91"/>
+  <dimension ref="A1:AC99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,17 +704,17 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -824,17 +824,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>88.0</t>
@@ -949,7 +949,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1287,22 +1287,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1535,12 +1535,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,22 +1882,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>94.6</t>
+          <t>97.1</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,22 +2001,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2235,22 +2235,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2479,12 +2479,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2588,17 +2588,17 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2707,22 +2707,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2950,17 +2950,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3298,14 +3298,14 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
           <t>88.0</t>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3536,22 +3536,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3903,12 +3903,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4012,22 +4012,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4131,22 +4131,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>94.6</t>
+          <t>97.1</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4374,12 +4374,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4612,17 +4612,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4972,14 +4972,14 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
           <t>88.0</t>
@@ -4987,7 +4987,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5101,12 +5101,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5456,22 +5456,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5575,22 +5575,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>94.6</t>
+          <t>97.1</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5699,12 +5699,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5937,17 +5937,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6170,14 +6170,14 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
           <t>88.0</t>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6299,12 +6299,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6418,12 +6418,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6527,22 +6527,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6646,22 +6646,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>94.6</t>
+          <t>97.1</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7008,17 +7008,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7241,14 +7241,14 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
           <t>88.0</t>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7360,17 +7360,17 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7717,22 +7717,22 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7836,22 +7836,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>94.6</t>
+          <t>97.1</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7955,22 +7955,22 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8074,22 +8074,22 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8203,12 +8203,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8431,22 +8431,22 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8511,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8669,7 +8669,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8798,12 +8798,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8912,17 +8912,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9106,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9193,7 +9193,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -9210,7 +9210,7 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站大同路石家街（市七医院） ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数10分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
@@ -9264,14 +9264,14 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
           <t>88.0</t>
@@ -9279,7 +9279,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9312,27 +9312,31 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：17:20采样，终点ETA 27分钟</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9340,7 +9344,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9364,12 +9368,12 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
@@ -9389,12 +9393,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9427,29 +9431,29 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站大同路石家街（市七医院） ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数9分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -9459,7 +9463,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9483,12 +9487,12 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
@@ -9498,17 +9502,17 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9546,24 +9550,24 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站金高路俱进路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
@@ -9578,7 +9582,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9602,12 +9606,12 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
@@ -9627,12 +9631,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -9665,29 +9669,29 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站五莲路荷泽路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9697,7 +9701,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9721,12 +9725,12 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
@@ -9736,22 +9740,22 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9784,24 +9788,24 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站巨峰路成园路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -9816,7 +9820,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9840,12 +9844,12 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
@@ -9855,22 +9859,22 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA79" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9903,27 +9907,31 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>103分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -9931,7 +9939,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9955,37 +9963,37 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>94.6</t>
+          <t>97.1</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -10018,27 +10026,31 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -10046,7 +10058,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10070,17 +10082,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10090,12 +10102,12 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10133,27 +10145,31 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>110分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -10161,7 +10177,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10185,37 +10201,37 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -10253,19 +10269,19 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站金杨路枣庄路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数72分钟，约±5分钟</t>
+          <t>18:00采样：该车到重点站金高路俱进路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
@@ -10280,7 +10296,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10329,12 +10345,12 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -10372,26 +10388,22 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站金高路俱进路 ETA 25分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±12分钟</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:20采样，终点ETA 26分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -10399,7 +10411,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10428,7 +10440,7 @@
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
@@ -10438,22 +10450,22 @@
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA84" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10491,19 +10503,19 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数96分钟估算，约±5分钟</t>
+          <t>18:20采样：该车到重点站杨高北路（外高桥保税区南站） ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -10518,7 +10530,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10547,7 +10559,7 @@
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
@@ -10567,12 +10579,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -10610,19 +10622,19 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数100分钟估算，约±5分钟</t>
+          <t>18:20采样：该车到重点站五莲路归昌路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -10637,7 +10649,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10666,7 +10678,7 @@
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
@@ -10676,7 +10688,7 @@
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA86" s="2" t="inlineStr">
@@ -10686,12 +10698,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -10729,19 +10741,19 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±5分钟</t>
+          <t>18:20采样：该车到重点站金高路行泰路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -10756,7 +10768,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10785,7 +10797,7 @@
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
@@ -10805,12 +10817,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -10871,7 +10883,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10963,22 +10975,26 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>111分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>18:20采样：该车到重点站张杨北路博兴路 ETA 40分钟；叠加该车自身同类时段从该站到终点历史中位数31分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -10986,7 +11002,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11010,17 +11026,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11030,17 +11046,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -11101,7 +11117,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11155,7 +11171,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -11216,7 +11232,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11265,10 +11281,942 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
+          <t>88.2</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>108分钟</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>18:20采样：该车到重点站张杨北路金桥路 ETA 20分钟；叠加该车自身同类时段从该站到终点历史中位数77分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>89.3</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
           <t>88.3</t>
         </is>
       </c>
-      <c r="AC91" s="2" t="inlineStr">
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>104分钟</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数104分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>97.1</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>90.7</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>105分钟</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数105分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>97.8</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>18/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>90.2</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
         <is>
           <t>9/18</t>
         </is>

--- a/data/export/2026-09-17-浦东78路.xlsx
+++ b/data/export/2026-09-17-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:AC103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,22 +704,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -939,17 +939,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1058,12 +1058,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1644,22 +1644,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1763,22 +1763,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>97.1</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2011,12 +2011,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2469,22 +2469,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2588,22 +2588,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2831,12 +2831,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3303,17 +3303,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3774,22 +3774,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3893,22 +3893,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4022,12 +4022,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>97.1</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4488,22 +4488,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4617,12 +4617,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4731,12 +4731,12 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4977,17 +4977,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5218,22 +5218,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5352,7 +5352,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>97.1</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5942,12 +5942,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6175,17 +6175,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6537,12 +6537,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>97.1</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7246,17 +7246,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7360,22 +7360,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7613,7 +7613,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7727,12 +7727,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>97.1</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8193,22 +8193,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8436,17 +8436,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -8511,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8788,22 +8788,22 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8917,12 +8917,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9026,22 +9026,22 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9106,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9269,17 +9269,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9344,7 +9344,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9463,7 +9463,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9502,22 +9502,22 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9636,7 +9636,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9701,7 +9701,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9750,12 +9750,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9820,7 +9820,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9874,7 +9874,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9988,7 +9988,7 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>97.1</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10043,12 +10043,12 @@
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10150,24 +10150,24 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>110分钟</t>
+          <t>107分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
@@ -10264,29 +10264,29 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>106分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>18:00采样：该车到重点站金高路俱进路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
@@ -10335,22 +10335,22 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA83" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -10383,7 +10383,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -10400,10 +10400,14 @@
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：18:20采样，终点ETA 26分钟</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -10411,7 +10415,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10435,12 +10439,12 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
@@ -10455,17 +10459,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -10498,24 +10502,24 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>109分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站杨高北路（外高桥保税区南站） ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -10530,7 +10534,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10554,12 +10558,12 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
@@ -10579,12 +10583,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -10617,24 +10621,24 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>102分钟</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站五莲路归昌路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -10649,7 +10653,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10673,12 +10677,12 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
@@ -10698,12 +10702,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10736,29 +10740,29 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>116分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站金高路行泰路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -10768,7 +10772,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10792,12 +10796,12 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
@@ -10807,22 +10811,22 @@
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -10855,27 +10859,31 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>106分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -10883,7 +10891,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10907,17 +10915,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10927,12 +10935,12 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -10970,29 +10978,29 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>111分钟</t>
+          <t>119分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站张杨北路博兴路 ETA 40分钟；叠加该车自身同类时段从该站到终点历史中位数31分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -11002,7 +11010,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11026,12 +11034,12 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
@@ -11051,12 +11059,12 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -11094,19 +11102,19 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>113分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：19:20采样，终点ETA 28分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr"/>
@@ -11117,7 +11125,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11141,37 +11149,37 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA90" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -11232,7 +11240,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11286,7 +11294,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -11324,22 +11332,26 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>108分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>19:20采样：该车到重点站五莲路荷泽路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -11347,7 +11359,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11371,17 +11383,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11391,17 +11403,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -11439,24 +11451,24 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>108分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站张杨北路金桥路 ETA 20分钟；叠加该车自身同类时段从该站到终点历史中位数77分钟，约±7分钟</t>
+          <t>19:20采样：该车到重点站大同路石家街（市七医院） ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数8分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -11466,7 +11478,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11515,12 +11527,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -11581,7 +11593,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11620,22 +11632,22 @@
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA94" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -11696,7 +11708,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11750,7 +11762,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -11788,24 +11800,24 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>104分钟</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数104分钟估算，约±5分钟</t>
+          <t>19:20采样：该车到重点站巨峰路成园路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11815,7 +11827,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11844,7 +11856,7 @@
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
@@ -11864,7 +11876,7 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>97.1</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
@@ -11907,22 +11919,26 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>19:20采样：该车到重点站巨峰路成园路 ETA 21分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -11930,7 +11946,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11954,17 +11970,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11974,17 +11990,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -12022,24 +12038,24 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>20:47</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>105分钟</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数105分钟估算，约±10分钟</t>
+          <t>19:20采样：该车到重点站金高路俱进路 ETA 21分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -12049,7 +12065,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12073,12 +12089,12 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
@@ -12098,7 +12114,7 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
@@ -12164,7 +12180,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12213,12 +12229,484 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>96.2</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>21:14</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>21:22</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>92.8</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>21:39</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>90.4</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-浦东78路.xlsx
+++ b/data/export/2026-09-17-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC103"/>
+  <dimension ref="A1:AC104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1287,22 +1287,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1530,17 +1530,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2011,12 +2011,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2240,17 +2240,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3536,22 +3536,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4022,12 +4022,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -4265,7 +4265,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4617,12 +4617,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5096,17 +5096,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5352,7 +5352,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5942,12 +5942,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6294,17 +6294,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6537,12 +6537,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -6899,7 +6899,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7484,17 +7484,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7613,7 +7613,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7727,12 +7727,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7960,17 +7960,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8074,22 +8074,22 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8917,12 +8917,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9388,17 +9388,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9463,7 +9463,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9701,7 +9701,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9750,12 +9750,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9820,7 +9820,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9864,17 +9864,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9993,7 +9993,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -10177,7 +10177,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10216,22 +10216,22 @@
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -10415,7 +10415,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10469,7 +10469,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -10588,7 +10588,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10653,7 +10653,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10707,7 +10707,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -10772,7 +10772,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -10983,24 +10983,24 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>119分钟</t>
+          <t>115分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -11010,7 +11010,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -11097,7 +11097,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -11114,10 +11114,14 @@
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：19:20采样，终点ETA 28分钟</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -11125,7 +11129,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11149,12 +11153,12 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
@@ -11179,7 +11183,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -11217,19 +11221,19 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>103分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：19:30采样，终点ETA 7分钟</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr"/>
@@ -11240,7 +11244,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11264,17 +11268,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11284,17 +11288,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -11359,7 +11363,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11451,26 +11455,22 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站大同路石家街（市七医院） ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数8分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：19:30采样，终点ETA 13分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -11478,7 +11478,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
@@ -11527,12 +11527,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -11593,7 +11593,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11685,22 +11685,26 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>19:30采样：该车到重点站大同路和龙路 ETA 21分钟；叠加该车自身同类时段从该站到终点历史中位数6分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>07:18</t>
@@ -11708,7 +11712,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11732,17 +11736,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11752,17 +11756,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -11812,12 +11816,12 @@
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站巨峰路成园路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±8分钟</t>
+          <t>19:30采样：该车到重点站张杨北路五莲路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11827,7 +11831,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11881,7 +11885,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -11946,7 +11950,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12000,7 +12004,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -12038,19 +12042,19 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>20:47</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>102分钟</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站金高路俱进路 ETA 21分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±11分钟</t>
+          <t>19:30采样：该车到重点站金高路万安街 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
@@ -12065,7 +12069,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12104,22 +12108,22 @@
       </c>
       <c r="Z98" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -12180,7 +12184,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12234,7 +12238,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -12295,7 +12299,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12349,7 +12353,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -12414,7 +12418,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12468,7 +12472,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -12533,7 +12537,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12587,7 +12591,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -12652,7 +12656,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12710,6 +12714,125 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>21:56</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>76分钟</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>92.5</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-17-浦东78路.xlsx
+++ b/data/export/2026-09-17-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC104"/>
+  <dimension ref="A1:AC106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -944,12 +944,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1177,17 +1177,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1644,22 +1644,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2469,22 +2469,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2593,17 +2593,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3184,17 +3184,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3779,17 +3779,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3893,22 +3893,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -4265,7 +4265,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4488,22 +4488,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4858,17 +4858,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5223,17 +5223,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -5352,7 +5352,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -6899,7 +6899,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7365,17 +7365,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7494,7 +7494,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7613,7 +7613,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8193,22 +8193,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8674,17 +8674,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8788,22 +8788,22 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8922,7 +8922,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9031,17 +9031,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9463,7 +9463,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9507,17 +9507,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9636,7 +9636,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -9820,7 +9820,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9988,12 +9988,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -10177,7 +10177,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10335,22 +10335,22 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -10415,7 +10415,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10464,12 +10464,12 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -10588,7 +10588,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -10653,7 +10653,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10697,17 +10697,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -10772,7 +10772,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10811,22 +10811,22 @@
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -11102,24 +11102,24 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>113分钟</t>
+          <t>110分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -11129,7 +11129,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11173,17 +11173,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -11331,29 +11331,29 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>108分钟</t>
+          <t>111分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站五莲路荷泽路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -11363,7 +11363,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11387,12 +11387,12 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
@@ -11412,12 +11412,12 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -11570,19 +11570,19 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：19:50采样，终点ETA 12分钟</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr"/>
@@ -11593,7 +11593,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11617,17 +11617,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11637,17 +11637,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -11680,7 +11680,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -11697,12 +11697,12 @@
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>19:30采样：该车到重点站大同路和龙路 ETA 21分钟；叠加该车自身同类时段从该站到终点历史中位数6分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
@@ -11804,26 +11804,22 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>98分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>19:30采样：该车到重点站张杨北路五莲路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±7分钟</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：20:00采样，终点ETA 6分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -11831,7 +11827,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11860,7 +11856,7 @@
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
@@ -11880,12 +11876,12 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -11918,29 +11914,29 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站巨峰路成园路 ETA 21分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -11950,7 +11946,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11974,12 +11970,12 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
@@ -11999,12 +11995,12 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -12042,26 +12038,22 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>98分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>19:30采样：该车到重点站金高路万安街 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±11分钟</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：20:20采样，终点ETA 6分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -12069,7 +12061,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12093,12 +12085,12 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
@@ -12118,12 +12110,12 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -12156,27 +12148,31 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:48</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -12184,7 +12180,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12208,17 +12204,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12228,17 +12224,17 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -12276,19 +12272,19 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：20:20采样，终点ETA 39分钟</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr"/>
@@ -12299,7 +12295,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12323,37 +12319,37 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -12391,26 +12387,22 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：20:20采样，终点ETA 59分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -12418,7 +12410,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12442,17 +12434,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12462,17 +12454,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -12510,24 +12502,24 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±12分钟</t>
+          <t>20:20采样：该车到重点站金高路东靖路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -12537,7 +12529,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12561,12 +12553,12 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
@@ -12576,22 +12568,22 @@
       </c>
       <c r="Z102" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -12641,7 +12633,7 @@
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±10分钟</t>
+          <t>20:20采样：该车到重点站张杨北路金桥路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
@@ -12656,7 +12648,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12685,7 +12677,7 @@
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
@@ -12700,17 +12692,17 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -12775,7 +12767,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12824,12 +12816,250 @@
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
+          <t>89.7</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>22:31</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
           <t>92.5</t>
         </is>
       </c>
-      <c r="AC104" s="2" t="inlineStr">
-        <is>
-          <t>12/18</t>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>23:01</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-浦东78路.xlsx
+++ b/data/export/2026-09-17-浦东78路.xlsx
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2479,12 +2479,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3779,17 +3779,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5223,17 +5223,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6899,7 +6899,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7370,12 +7370,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7494,7 +7494,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8565,7 +8565,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8798,12 +8798,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8922,7 +8922,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9031,17 +9031,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -9279,7 +9279,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9463,7 +9463,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9512,12 +9512,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -10177,7 +10177,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10345,7 +10345,7 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10653,7 +10653,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10702,12 +10702,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -10772,7 +10772,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10821,12 +10821,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -11129,7 +11129,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11173,17 +11173,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -11417,7 +11417,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -11593,7 +11593,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11642,12 +11642,12 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -12061,7 +12061,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12110,12 +12110,12 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -12153,24 +12153,24 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>20:48</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -12180,7 +12180,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12229,12 +12229,12 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -12267,27 +12267,31 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:20采样，终点ETA 39分钟</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -12295,7 +12299,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12319,12 +12323,12 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
@@ -12344,7 +12348,7 @@
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
@@ -12382,27 +12386,31 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>21:19</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:20采样，终点ETA 59分钟</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -12410,7 +12418,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12434,17 +12442,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12454,17 +12462,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -12497,29 +12505,29 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站金高路东靖路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -12529,7 +12537,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12553,12 +12561,12 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
@@ -12578,12 +12586,12 @@
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -12621,26 +12629,22 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>21:39</t>
+          <t>21:34</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站张杨北路金桥路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±10分钟</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:20采样，终点ETA 14分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -12648,7 +12652,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12677,7 +12681,7 @@
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
@@ -12697,12 +12701,12 @@
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -12740,26 +12744,22 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>21:56</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:20采样，终点ETA 42分钟</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
       <c r="N104" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12791,12 +12791,12 @@
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X104" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y104" s="2" t="inlineStr">
@@ -12816,12 +12816,12 @@
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -12859,24 +12859,24 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±10分钟</t>
+          <t>21:20采样：该车到重点站金杨路枣庄路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±14分钟</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -12886,7 +12886,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12910,12 +12910,12 @@
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X105" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y105" s="2" t="inlineStr">
@@ -12935,7 +12935,7 @@
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
@@ -13005,7 +13005,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13054,12 +13054,12 @@
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-浦东78路.xlsx
+++ b/data/export/2026-09-17-浦东78路.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2479,12 +2479,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3903,12 +3903,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4265,7 +4265,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6899,7 +6899,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7370,12 +7370,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7494,7 +7494,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8203,12 +8203,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8798,12 +8798,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9279,7 +9279,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9463,7 +9463,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9512,12 +9512,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -10177,7 +10177,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10345,12 +10345,12 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -10588,7 +10588,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -10772,7 +10772,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10821,12 +10821,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -11417,7 +11417,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -11593,7 +11593,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11642,12 +11642,12 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -12061,7 +12061,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12110,12 +12110,12 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -12299,7 +12299,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12348,12 +12348,12 @@
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -12537,7 +12537,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12586,12 +12586,12 @@
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -12624,27 +12624,31 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>21:34</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：21:20采样，终点ETA 14分钟</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -12652,7 +12656,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12676,12 +12680,12 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
@@ -12701,12 +12705,12 @@
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -12739,27 +12743,31 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>22:02</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：21:20采样，终点ETA 42分钟</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -12767,7 +12775,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12791,12 +12799,12 @@
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X104" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y104" s="2" t="inlineStr">
@@ -12816,12 +12824,12 @@
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -12854,29 +12862,29 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站金杨路枣庄路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±14分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -12886,7 +12894,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12910,12 +12918,12 @@
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X105" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y105" s="2" t="inlineStr">
@@ -12935,12 +12943,12 @@
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -12983,14 +12991,14 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±5分钟</t>
+          <t>21:50采样：该车到重点站金杨路云山路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
@@ -13005,7 +13013,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13034,7 +13042,7 @@
       </c>
       <c r="X106" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y106" s="2" t="inlineStr">
@@ -13054,12 +13062,12 @@
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
